--- a/artfynd/A 7672-2023 artfynd.xlsx
+++ b/artfynd/A 7672-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7672-2023 artfynd.xlsx
+++ b/artfynd/A 7672-2023 artfynd.xlsx
@@ -1370,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121179070</v>
+        <v>121179035</v>
       </c>
       <c r="B8" t="n">
-        <v>98071</v>
+        <v>79683</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,32 +1382,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Högberget, Jmt</t>
@@ -1449,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,7 +1455,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121179627</v>
+        <v>121179994</v>
       </c>
       <c r="B9" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,28 +1494,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Högberget, Jmt</t>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121179035</v>
+        <v>121178118</v>
       </c>
       <c r="B10" t="n">
-        <v>79680</v>
+        <v>78601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,7 +1713,7 @@
         <v>121179820</v>
       </c>
       <c r="B11" t="n">
-        <v>92160</v>
+        <v>92170</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121179038</v>
+        <v>121179725</v>
       </c>
       <c r="B12" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,7 +1937,7 @@
         <v>121179682</v>
       </c>
       <c r="B13" t="n">
-        <v>78632</v>
+        <v>78635</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>121178293</v>
       </c>
       <c r="B14" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 7672-2023 artfynd.xlsx
+++ b/artfynd/A 7672-2023 artfynd.xlsx
@@ -1482,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121179994</v>
+        <v>121178118</v>
       </c>
       <c r="B9" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,32 +1494,28 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Högberget, Jmt</t>
@@ -1561,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121178118</v>
+        <v>121179994</v>
       </c>
       <c r="B10" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,28 +1606,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Högberget, Jmt</t>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 7672-2023 artfynd.xlsx
+++ b/artfynd/A 7672-2023 artfynd.xlsx
@@ -1370,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121179035</v>
+        <v>121179973</v>
       </c>
       <c r="B8" t="n">
-        <v>79683</v>
+        <v>98081</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,28 +1382,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Högberget, Jmt</t>
@@ -1445,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1459,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121178118</v>
+        <v>121179682</v>
       </c>
       <c r="B9" t="n">
-        <v>78601</v>
+        <v>78635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,21 +1502,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1557,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121179994</v>
+        <v>121179038</v>
       </c>
       <c r="B10" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,32 +1610,28 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Högberget, Jmt</t>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121179820</v>
+        <v>121179627</v>
       </c>
       <c r="B11" t="n">
-        <v>92170</v>
+        <v>78601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121179725</v>
+        <v>121179035</v>
       </c>
       <c r="B12" t="n">
-        <v>79682</v>
+        <v>79683</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,10 +1934,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121179682</v>
+        <v>121179820</v>
       </c>
       <c r="B13" t="n">
-        <v>78635</v>
+        <v>92170</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1950,21 +1950,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>2079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 7672-2023 artfynd.xlsx
+++ b/artfynd/A 7672-2023 artfynd.xlsx
@@ -1370,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121179973</v>
+        <v>121179105</v>
       </c>
       <c r="B8" t="n">
-        <v>98081</v>
+        <v>78604</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,32 +1382,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Högberget, Jmt</t>
@@ -1449,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,7 +1455,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121179682</v>
+        <v>121179973</v>
       </c>
       <c r="B9" t="n">
-        <v>78635</v>
+        <v>98094</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,28 +1494,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Högberget, Jmt</t>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121179038</v>
+        <v>121179725</v>
       </c>
       <c r="B10" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121179627</v>
+        <v>121179820</v>
       </c>
       <c r="B11" t="n">
-        <v>78601</v>
+        <v>92182</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,7 +1825,7 @@
         <v>121179035</v>
       </c>
       <c r="B12" t="n">
-        <v>79683</v>
+        <v>79686</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121179820</v>
+        <v>121179682</v>
       </c>
       <c r="B13" t="n">
-        <v>92170</v>
+        <v>78638</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1950,21 +1950,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2079</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 7672-2023 artfynd.xlsx
+++ b/artfynd/A 7672-2023 artfynd.xlsx
@@ -1370,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121179105</v>
+        <v>121179725</v>
       </c>
       <c r="B8" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,21 +1386,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121179973</v>
+        <v>121179105</v>
       </c>
       <c r="B9" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,32 +1494,28 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Högberget, Jmt</t>
@@ -1561,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121179725</v>
+        <v>121179820</v>
       </c>
       <c r="B10" t="n">
-        <v>79685</v>
+        <v>92183</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1614,21 +1610,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1673,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121179820</v>
+        <v>121179973</v>
       </c>
       <c r="B11" t="n">
-        <v>92182</v>
+        <v>98095</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,28 +1718,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Högberget, Jmt</t>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121179035</v>
+        <v>121179682</v>
       </c>
       <c r="B12" t="n">
-        <v>79686</v>
+        <v>78638</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,10 +1934,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121179682</v>
+        <v>121179035</v>
       </c>
       <c r="B13" t="n">
-        <v>78638</v>
+        <v>79686</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1950,21 +1950,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 7672-2023 artfynd.xlsx
+++ b/artfynd/A 7672-2023 artfynd.xlsx
@@ -1370,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121179725</v>
+        <v>121180135</v>
       </c>
       <c r="B8" t="n">
-        <v>79685</v>
+        <v>78607</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,21 +1386,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121179105</v>
+        <v>121180092</v>
       </c>
       <c r="B9" t="n">
-        <v>78604</v>
+        <v>98098</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,28 +1494,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Högberget, Jmt</t>
@@ -1557,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1597,7 +1601,7 @@
         <v>121179820</v>
       </c>
       <c r="B10" t="n">
-        <v>92183</v>
+        <v>92186</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1706,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121179973</v>
+        <v>121179725</v>
       </c>
       <c r="B11" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,32 +1722,28 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Högberget, Jmt</t>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121179682</v>
+        <v>121179035</v>
       </c>
       <c r="B12" t="n">
-        <v>78638</v>
+        <v>79689</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,10 +1934,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121179035</v>
+        <v>121179682</v>
       </c>
       <c r="B13" t="n">
-        <v>79686</v>
+        <v>78641</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1950,21 +1950,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,7 +2049,7 @@
         <v>121178293</v>
       </c>
       <c r="B14" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 7672-2023 artfynd.xlsx
+++ b/artfynd/A 7672-2023 artfynd.xlsx
@@ -1370,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121180135</v>
+        <v>121179820</v>
       </c>
       <c r="B8" t="n">
-        <v>78607</v>
+        <v>92186</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,21 +1386,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121180092</v>
+        <v>121179935</v>
       </c>
       <c r="B9" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,32 +1494,28 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Högberget, Jmt</t>
@@ -1561,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121179820</v>
+        <v>121180092</v>
       </c>
       <c r="B10" t="n">
-        <v>92186</v>
+        <v>98098</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,28 +1606,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Högberget, Jmt</t>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 7672-2023 artfynd.xlsx
+++ b/artfynd/A 7672-2023 artfynd.xlsx
@@ -1370,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121179820</v>
+        <v>121179935</v>
       </c>
       <c r="B8" t="n">
-        <v>92186</v>
+        <v>78607</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,21 +1386,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121179935</v>
+        <v>121179820</v>
       </c>
       <c r="B9" t="n">
-        <v>78607</v>
+        <v>92186</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,21 +1498,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 7672-2023 artfynd.xlsx
+++ b/artfynd/A 7672-2023 artfynd.xlsx
@@ -1370,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121179935</v>
+        <v>121179820</v>
       </c>
       <c r="B8" t="n">
-        <v>78607</v>
+        <v>92186</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,21 +1386,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121179820</v>
+        <v>121179935</v>
       </c>
       <c r="B9" t="n">
-        <v>92186</v>
+        <v>78607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,21 +1498,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 7672-2023 artfynd.xlsx
+++ b/artfynd/A 7672-2023 artfynd.xlsx
@@ -1370,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121179820</v>
+        <v>121179994</v>
       </c>
       <c r="B8" t="n">
-        <v>92186</v>
+        <v>98104</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,28 +1382,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Högberget, Jmt</t>
@@ -1445,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1459,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121179935</v>
+        <v>121179682</v>
       </c>
       <c r="B9" t="n">
-        <v>78607</v>
+        <v>78642</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,21 +1502,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1557,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121180092</v>
+        <v>121179820</v>
       </c>
       <c r="B10" t="n">
-        <v>98098</v>
+        <v>92192</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,32 +1610,28 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Högberget, Jmt</t>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121179725</v>
+        <v>121179935</v>
       </c>
       <c r="B11" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,7 +1825,7 @@
         <v>121179035</v>
       </c>
       <c r="B12" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121179682</v>
+        <v>121179038</v>
       </c>
       <c r="B13" t="n">
-        <v>78641</v>
+        <v>79689</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1950,21 +1950,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,7 +2049,7 @@
         <v>121178293</v>
       </c>
       <c r="B14" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 7672-2023 artfynd.xlsx
+++ b/artfynd/A 7672-2023 artfynd.xlsx
@@ -2049,7 +2049,7 @@
         <v>121178293</v>
       </c>
       <c r="B14" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
